--- a/.files/test_Report.xlsx
+++ b/.files/test_Report.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00_-"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,9 +46,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <i val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -164,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -202,8 +199,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1642,7 +1637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -3090,153 +3085,215 @@
       <c r="C42" s="26" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="27" t="inlineStr">
-        <is>
-          <t>(None configured)</t>
-        </is>
-      </c>
-      <c r="C43" s="28" t="n"/>
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>Overhead Materials</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="n">
+        <v>184.653625</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="29" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="B44" s="30" t="n"/>
-      <c r="C44" s="31" t="n">
-        <v>0</v>
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t>Overhead Labor</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="n">
+        <v>184.653625</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="32" t="inlineStr">
-        <is>
-          <t>MARKUPS / PROFIT</t>
-        </is>
-      </c>
-      <c r="B45" s="33" t="n"/>
-      <c r="C45" s="34" t="n"/>
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>Admin and Management</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="n">
+        <v>184.653625</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t>Profit on Material</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C46" s="18" t="n">
-        <v>122.684875</v>
+        <v>184.653625</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t>Profit on Waste</t>
+          <t>Packaging Materials</t>
         </is>
       </c>
       <c r="C47" s="18" t="n">
-        <v>56.54223666666667</v>
+        <v>184.653625</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>Profit on Glass Purchase</t>
+          <t>Shipping and Transport</t>
         </is>
       </c>
       <c r="C48" s="18" t="n">
-        <v>43.96875</v>
+        <v>184.653625</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="17" t="inlineStr">
         <is>
-          <t>Profit on Wages</t>
+          <t>Commissions</t>
         </is>
       </c>
       <c r="C49" s="18" t="n">
-        <v>18</v>
+        <v>184.653625</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="inlineStr">
-        <is>
-          <t>Planning / Technical Office</t>
-        </is>
-      </c>
-      <c r="C50" s="18" t="n">
-        <v>184.653625</v>
+      <c r="A50" s="27" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B50" s="28" t="n"/>
+      <c r="C50" s="29" t="n">
+        <v>1292.575375</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="17" t="inlineStr">
-        <is>
-          <t>Commission</t>
-        </is>
-      </c>
-      <c r="C51" s="18" t="n">
-        <v>184.653625</v>
-      </c>
+      <c r="A51" s="30" t="inlineStr">
+        <is>
+          <t>MARKUPS / PROFIT</t>
+        </is>
+      </c>
+      <c r="B51" s="31" t="n"/>
+      <c r="C51" s="32" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="29" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="B52" s="30" t="n"/>
-      <c r="C52" s="31" t="n">
-        <v>610.5031116666668</v>
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>Profit on Material</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="n">
+        <v>122.684875</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="35" t="inlineStr">
-        <is>
-          <t>PROJECT TOTAL</t>
-        </is>
-      </c>
-      <c r="B53" s="36" t="n"/>
-      <c r="C53" s="37" t="n"/>
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>Profit on Waste</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="n">
+        <v>56.54223666666667</v>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="38" t="inlineStr">
-        <is>
-          <t>Discounted Total:</t>
-        </is>
-      </c>
-      <c r="B54" s="39" t="n"/>
-      <c r="C54" s="40" t="n">
-        <v>3693.0725</v>
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>Profit on Glass Purchase</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="n">
+        <v>43.96875</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="17" t="inlineStr">
         <is>
-          <t>+ Miscellaneous:</t>
+          <t>Profit on Wages</t>
         </is>
       </c>
       <c r="C55" s="18" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="17" t="inlineStr">
         <is>
+          <t>Planning / Technical Office</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="n">
+        <v>184.653625</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="17" t="inlineStr">
+        <is>
+          <t>Commission</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="n">
+        <v>184.653625</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="27" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B58" s="28" t="n"/>
+      <c r="C58" s="29" t="n">
+        <v>610.5031116666668</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="33" t="inlineStr">
+        <is>
+          <t>PROJECT TOTAL</t>
+        </is>
+      </c>
+      <c r="B59" s="34" t="n"/>
+      <c r="C59" s="35" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="36" t="inlineStr">
+        <is>
+          <t>Discounted Total:</t>
+        </is>
+      </c>
+      <c r="B60" s="37" t="n"/>
+      <c r="C60" s="38" t="n">
+        <v>3693.0725</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="17" t="inlineStr">
+        <is>
+          <t>+ Miscellaneous:</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="n">
+        <v>1292.575375</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="inlineStr">
+        <is>
           <t>+ Markups:</t>
         </is>
       </c>
-      <c r="C56" s="18" t="n">
+      <c r="C62" s="18" t="n">
         <v>610.5031116666668</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="41" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="39" t="inlineStr">
         <is>
           <t>GRAND TOTAL:</t>
         </is>
       </c>
-      <c r="B57" s="42" t="n"/>
-      <c r="C57" s="43" t="n">
-        <v>4303.575611666667</v>
+      <c r="B63" s="40" t="n"/>
+      <c r="C63" s="41" t="n">
+        <v>5596.150986666667</v>
       </c>
     </row>
   </sheetData>

--- a/.files/test_Report.xlsx
+++ b/.files/test_Report.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00_-"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,16 +37,19 @@
       <sz val="12"/>
     </font>
     <font>
-      <sz val="12"/>
+      <i val="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <i val="1"/>
-      <sz val="10"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -161,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -174,12 +178,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -199,6 +203,8 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -297,7 +303,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -312,13 +318,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -327,7 +333,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -342,13 +348,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -645,6 +651,343 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="68" customWidth="1" min="2" max="2"/>
+    <col width="2" customWidth="1" min="3" max="3"/>
+    <col width="2" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="2" customWidth="1" min="10" max="10"/>
+    <col width="2" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>System Input</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Door Only</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>DOORS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Finish</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Elevation Type</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Door (3' X 8')</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1.00 pcs</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>2258.25</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>2258.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Total Count</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Total Door Cost</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>2258.25</v>
+      </c>
+      <c r="I4" s="9" t="n">
+        <v>2258.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Bays Wide</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr"/>
+      <c r="B6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Custom Bay Widths</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Equal distribution</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>COST/ELEVATION</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL ELEVATION COST</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Custom Bay Heights</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Equal distribution</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>PROFILE COSTS</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Opening Width</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>36.00 in</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ACCESSORY COSTS</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Opening Height</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>96.00 in</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>GASKET COSTS</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Sq Ft per Type</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>24.00 sqft</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>DOOR COSTS</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>2258.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Total Sq Ft</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>24.00 sqft</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>GLASS COSTS</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Perimeter Ft</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>22.00 ft</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FABRICATION COSTS</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Total Perimeter Ft</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>22.00 ft</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Doors</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>1 x Medium Door ($2,258.25)
+  with: Exit Devices, Concealed Closer</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>1 TOTAL COSTS</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>2258.25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>*Note - Elevation costs based on discounted material costs</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -655,7 +998,7 @@
     <col width="99" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="2" customWidth="1" min="10" max="10"/>
     <col width="2" customWidth="1" min="11" max="11"/>
@@ -686,7 +1029,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -723,7 +1066,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -742,10 +1085,10 @@
         </is>
       </c>
       <c r="H3" s="5" t="n">
-        <v>838</v>
+        <v>921.8000000000002</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>514.532</v>
+        <v>565.9852000000001</v>
       </c>
     </row>
     <row r="4">
@@ -773,10 +1116,10 @@
         </is>
       </c>
       <c r="H4" s="5" t="n">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>92.09999999999999</v>
+        <v>101.31</v>
       </c>
     </row>
     <row r="5">
@@ -804,10 +1147,10 @@
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>497</v>
+        <v>546.7</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>305.158</v>
+        <v>335.6738</v>
       </c>
     </row>
     <row r="6">
@@ -835,10 +1178,10 @@
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>527</v>
+        <v>579.7</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>323.578</v>
+        <v>355.9358</v>
       </c>
     </row>
     <row r="7">
@@ -868,10 +1211,10 @@
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>444</v>
+        <v>488.4</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>272.616</v>
+        <v>299.8776</v>
       </c>
     </row>
     <row r="8">
@@ -901,10 +1244,10 @@
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>264</v>
+        <v>290.4</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>162.096</v>
+        <v>178.3056</v>
       </c>
     </row>
     <row r="9">
@@ -934,10 +1277,10 @@
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>85.05</v>
+        <v>93.55500000000001</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>52.2207</v>
+        <v>57.44277</v>
       </c>
     </row>
     <row r="10">
@@ -959,10 +1302,10 @@
         </is>
       </c>
       <c r="H10" s="9" t="n">
-        <v>2805.05</v>
+        <v>3085.555</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>1722.3007</v>
+        <v>1894.53077</v>
       </c>
     </row>
     <row r="11">
@@ -1147,7 +1490,7 @@
           <t>Bay Distribution Diagram</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>*Note - C/L Dimensions</t>
         </is>
@@ -1565,7 +1908,7 @@
         </is>
       </c>
       <c r="I39" s="5" t="n">
-        <v>1722.3007</v>
+        <v>1894.53077</v>
       </c>
     </row>
     <row r="40">
@@ -1609,17 +1952,17 @@
       </c>
     </row>
     <row r="44">
-      <c r="G44" s="11" t="inlineStr">
-        <is>
-          <t>1 TOTAL COSTS</t>
-        </is>
-      </c>
-      <c r="I44" s="12" t="n">
-        <v>3693.0725</v>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>2 TOTAL COSTS</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="n">
+        <v>3865.30257</v>
       </c>
     </row>
     <row r="45">
-      <c r="G45" s="13" t="inlineStr">
+      <c r="G45" s="12" t="inlineStr">
         <is>
           <t>*Note - Elevation costs based on discounted material costs</t>
         </is>
@@ -1631,13 +1974,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -1645,7 +1988,7 @@
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -1719,7 +2062,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BE9-2513 (clear)</t>
+          <t>BE9-2513 (black)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1738,10 +2081,10 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>838</v>
+        <v>921.8000000000002</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>514.532</v>
+        <v>565.9852000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1754,7 +2097,7 @@
         </is>
       </c>
       <c r="J3" s="5" t="n">
-        <v>214.3883333333333</v>
+        <v>235.8271666666667</v>
       </c>
     </row>
     <row r="4">
@@ -1765,7 +2108,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>E9-2512 (clear)</t>
+          <t>E9-2512 (black)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1784,10 +2127,10 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>92.09999999999999</v>
+        <v>101.31</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1811,7 +2154,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BE9-2511 (clear)</t>
+          <t>BE9-2511 (black)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1830,10 +2173,10 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>497</v>
+        <v>546.7</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>305.158</v>
+        <v>335.6738</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1857,7 +2200,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BE9-2515 (clear)</t>
+          <t>BE9-2515 (black)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1876,10 +2219,10 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>527</v>
+        <v>579.7</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>323.578</v>
+        <v>355.9358</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1892,7 +2235,7 @@
         </is>
       </c>
       <c r="J6" s="5" t="n">
-        <v>161.789</v>
+        <v>177.9679</v>
       </c>
     </row>
     <row r="7">
@@ -1903,7 +2246,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BE9-2514 (clear)</t>
+          <t>BE9-2514 (black)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1922,10 +2265,10 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>444</v>
+        <v>488.4</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>272.616</v>
+        <v>299.8776</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1938,7 +2281,7 @@
         </is>
       </c>
       <c r="J7" s="5" t="n">
-        <v>136.308</v>
+        <v>149.9388</v>
       </c>
     </row>
     <row r="8">
@@ -1949,7 +2292,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BE9-2578 (clear)</t>
+          <t>BE9-2578 (black)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1968,10 +2311,10 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>264</v>
+        <v>290.4</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>162.096</v>
+        <v>178.3056</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1984,7 +2327,7 @@
         </is>
       </c>
       <c r="J8" s="5" t="n">
-        <v>81.048</v>
+        <v>89.15280000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1995,7 +2338,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>E9-2519 (clear)</t>
+          <t>E9-2519 (black)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2014,10 +2357,10 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>85.05</v>
+        <v>93.55500000000001</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>52.2207</v>
+        <v>57.44277</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -2044,15 +2387,15 @@
         </is>
       </c>
       <c r="F10" s="9" t="n">
-        <v>2805.05</v>
+        <v>3085.555</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>1722.3007</v>
+        <v>1894.53077</v>
       </c>
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="7" t="n"/>
       <c r="J10" s="9" t="n">
-        <v>593.5333333333333</v>
+        <v>652.8866666666668</v>
       </c>
     </row>
     <row r="11">
@@ -2709,7 +3052,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>E2-0052 (clear)</t>
+          <t>E2-0052 (black)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2772,7 +3115,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>GLASS</t>
+          <t>DOORS</t>
         </is>
       </c>
     </row>
@@ -2831,12 +3174,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Glass Area (Adjusted)</t>
+          <t>Door (3' X 8')</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Glass Area (Adjusted)</t>
+          <t>Door (3' X 8')</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2846,19 +3189,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>$10.50</t>
+          <t>$2258.25</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>83.75 sqft</t>
+          <t>1.00 pcs</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>879.375</v>
+        <v>2258.25</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>879.375</v>
+        <v>2258.25</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2881,14 +3224,14 @@
       <c r="D32" s="7" t="n"/>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Total Glass Cost</t>
+          <t>Total Door Cost</t>
         </is>
       </c>
       <c r="F32" s="9" t="n">
-        <v>879.375</v>
+        <v>2258.25</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>879.375</v>
+        <v>2258.25</v>
       </c>
       <c r="H32" s="7" t="n"/>
       <c r="I32" s="7" t="n"/>
@@ -2899,7 +3242,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>LABOR</t>
+          <t>GLASS</t>
         </is>
       </c>
     </row>
@@ -2958,12 +3301,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Joints Fabrication Labor</t>
+          <t>Glass Area (Adjusted)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Joints Fabrication Labor</t>
+          <t>Glass Area (Adjusted)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2973,19 +3316,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>$10.50</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>24.00 joints</t>
+          <t>83.75 sqft</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>360</v>
+        <v>879.375</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>360</v>
+        <v>879.375</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -3008,14 +3351,14 @@
       <c r="D36" s="7" t="n"/>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Total Labor Cost</t>
+          <t>Total Glass Cost</t>
         </is>
       </c>
       <c r="F36" s="9" t="n">
-        <v>360</v>
+        <v>879.375</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>360</v>
+        <v>879.375</v>
       </c>
       <c r="H36" s="7" t="n"/>
       <c r="I36" s="7" t="n"/>
@@ -3024,276 +3367,289 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>LABOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Project Total Materials</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Unit Price</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Residual Material Quantity</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Residual Waste %</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>Residual Material Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Joints Fabrication Labor</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Joints Fabrication Labor</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>$15.00</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>24.00 joints</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>360</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>360</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n"/>
+      <c r="B40" s="7" t="n"/>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>Total Labor Cost</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>360</v>
+      </c>
+      <c r="G40" s="9" t="n">
+        <v>360</v>
+      </c>
+      <c r="H40" s="7" t="n"/>
+      <c r="I40" s="7" t="n"/>
+      <c r="J40" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>COST OVERVIEW</t>
         </is>
       </c>
-      <c r="B37" s="15" t="n"/>
-      <c r="C37" s="16" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="B41" s="15" t="n"/>
+      <c r="C41" s="16" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>List Price Total:</t>
         </is>
       </c>
-      <c r="C38" s="18" t="n">
-        <v>5235.625</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="19" t="inlineStr">
+      <c r="C42" s="18" t="n">
+        <v>7774.38</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>Discounted Total:</t>
         </is>
       </c>
-      <c r="C39" s="20" t="n">
-        <v>3693.0725</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>Residual/Waste Cost:</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="n">
-        <v>1130.844733333333</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="21" t="inlineStr">
-        <is>
-          <t>Waste Percentage:</t>
-        </is>
-      </c>
-      <c r="B41" s="22" t="n"/>
-      <c r="C41" s="23" t="inlineStr">
-        <is>
-          <t>30.62%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="24" t="inlineStr">
-        <is>
-          <t>MISCELLANEOUS COSTS</t>
-        </is>
-      </c>
-      <c r="B42" s="25" t="n"/>
-      <c r="C42" s="26" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>Overhead Materials</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="n">
-        <v>184.653625</v>
+      <c r="C43" s="20" t="n">
+        <v>6123.55257</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t>Overhead Labor</t>
+          <t>Residual/Waste Cost:</t>
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>184.653625</v>
+        <v>1190.198066666667</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="inlineStr">
-        <is>
-          <t>Admin and Management</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="n">
-        <v>184.653625</v>
+      <c r="A45" s="21" t="inlineStr">
+        <is>
+          <t>Waste Percentage:</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="n"/>
+      <c r="C45" s="23" t="inlineStr">
+        <is>
+          <t>19.44%</t>
+        </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="17" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="C46" s="18" t="n">
-        <v>184.653625</v>
-      </c>
+      <c r="A46" s="24" t="inlineStr">
+        <is>
+          <t>MISCELLANEOUS COSTS</t>
+        </is>
+      </c>
+      <c r="B46" s="25" t="n"/>
+      <c r="C46" s="26" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="17" t="inlineStr">
-        <is>
-          <t>Packaging Materials</t>
-        </is>
-      </c>
-      <c r="C47" s="18" t="n">
-        <v>184.653625</v>
-      </c>
+      <c r="A47" s="27" t="inlineStr">
+        <is>
+          <t>(None configured)</t>
+        </is>
+      </c>
+      <c r="C47" s="28" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="17" t="inlineStr">
-        <is>
-          <t>Shipping and Transport</t>
-        </is>
-      </c>
-      <c r="C48" s="18" t="n">
-        <v>184.653625</v>
+      <c r="A48" s="29" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B48" s="30" t="n"/>
+      <c r="C48" s="31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="17" t="inlineStr">
-        <is>
-          <t>Commissions</t>
-        </is>
-      </c>
-      <c r="C49" s="18" t="n">
-        <v>184.653625</v>
-      </c>
+      <c r="A49" s="32" t="inlineStr">
+        <is>
+          <t>MARKUPS / PROFIT</t>
+        </is>
+      </c>
+      <c r="B49" s="33" t="n"/>
+      <c r="C49" s="34" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="27" t="inlineStr">
         <is>
+          <t>(None configured)</t>
+        </is>
+      </c>
+      <c r="C50" s="28" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="29" t="inlineStr">
+        <is>
           <t>SUBTOTAL</t>
         </is>
       </c>
-      <c r="B50" s="28" t="n"/>
-      <c r="C50" s="29" t="n">
-        <v>1292.575375</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="30" t="inlineStr">
-        <is>
-          <t>MARKUPS / PROFIT</t>
-        </is>
-      </c>
-      <c r="B51" s="31" t="n"/>
-      <c r="C51" s="32" t="n"/>
+      <c r="B51" s="30" t="n"/>
+      <c r="C51" s="31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="17" t="inlineStr">
-        <is>
-          <t>Profit on Material</t>
-        </is>
-      </c>
-      <c r="C52" s="18" t="n">
-        <v>122.684875</v>
-      </c>
+      <c r="A52" s="35" t="inlineStr">
+        <is>
+          <t>PROJECT TOTAL</t>
+        </is>
+      </c>
+      <c r="B52" s="36" t="n"/>
+      <c r="C52" s="37" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="17" t="inlineStr">
-        <is>
-          <t>Profit on Waste</t>
-        </is>
-      </c>
-      <c r="C53" s="18" t="n">
-        <v>56.54223666666667</v>
+      <c r="A53" s="38" t="inlineStr">
+        <is>
+          <t>Discounted Total:</t>
+        </is>
+      </c>
+      <c r="B53" s="39" t="n"/>
+      <c r="C53" s="40" t="n">
+        <v>6123.55257</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="17" t="inlineStr">
         <is>
-          <t>Profit on Glass Purchase</t>
+          <t>+ Miscellaneous:</t>
         </is>
       </c>
       <c r="C54" s="18" t="n">
-        <v>43.96875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="17" t="inlineStr">
         <is>
-          <t>Profit on Wages</t>
+          <t>+ Markups:</t>
         </is>
       </c>
       <c r="C55" s="18" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="17" t="inlineStr">
-        <is>
-          <t>Planning / Technical Office</t>
-        </is>
-      </c>
-      <c r="C56" s="18" t="n">
-        <v>184.653625</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="17" t="inlineStr">
-        <is>
-          <t>Commission</t>
-        </is>
-      </c>
-      <c r="C57" s="18" t="n">
-        <v>184.653625</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="27" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="B58" s="28" t="n"/>
-      <c r="C58" s="29" t="n">
-        <v>610.5031116666668</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="33" t="inlineStr">
-        <is>
-          <t>PROJECT TOTAL</t>
-        </is>
-      </c>
-      <c r="B59" s="34" t="n"/>
-      <c r="C59" s="35" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="36" t="inlineStr">
-        <is>
-          <t>Discounted Total:</t>
-        </is>
-      </c>
-      <c r="B60" s="37" t="n"/>
-      <c r="C60" s="38" t="n">
-        <v>3693.0725</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="17" t="inlineStr">
-        <is>
-          <t>+ Miscellaneous:</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="n">
-        <v>1292.575375</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="17" t="inlineStr">
-        <is>
-          <t>+ Markups:</t>
-        </is>
-      </c>
-      <c r="C62" s="18" t="n">
-        <v>610.5031116666668</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="39" t="inlineStr">
+      <c r="A56" s="41" t="inlineStr">
         <is>
           <t>GRAND TOTAL:</t>
         </is>
       </c>
-      <c r="B63" s="40" t="n"/>
-      <c r="C63" s="41" t="n">
-        <v>5596.150986666667</v>
+      <c r="B56" s="42" t="n"/>
+      <c r="C56" s="43" t="n">
+        <v>6123.55257</v>
       </c>
     </row>
   </sheetData>

--- a/.files/test_Report.xlsx
+++ b/.files/test_Report.xlsx
@@ -1,15 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37,11 +36,11 @@
       <sz val="12"/>
     </font>
     <font>
+      <sz val="12"/>
+    </font>
+    <font>
       <i val="1"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
@@ -178,12 +177,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -303,7 +302,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -318,13 +317,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -333,7 +332,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -348,13 +347,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -651,14 +650,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="68" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="2" customWidth="1" min="3" max="3"/>
     <col width="2" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="99" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
@@ -675,12 +674,12 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Door Only</t>
+          <t>YES 45TU FRONT SET(OG)</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>DOORS</t>
+          <t>PROFILES</t>
         </is>
       </c>
     </row>
@@ -734,24 +733,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Door (3' X 8')</t>
+          <t>Vertical Sill/Jamb Screw Spline Assembly (Jamb) / Horizontal Sill/Jamb Screw Spline Assembly (Sill)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BE9-2513</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.00 pcs</t>
+          <t>8ft, 8ft, 3ft, 3ft, 3ft, 3ft</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
-        <v>2258.25</v>
+        <v>838</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>2258.25</v>
+        <v>514.532</v>
       </c>
     </row>
     <row r="4">
@@ -763,18 +762,26 @@
       <c r="B4" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Total Door Cost</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>2258.25</v>
-      </c>
-      <c r="I4" s="9" t="n">
-        <v>2258.25</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Vertical Flush Filler</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>E9-2512</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8ft x 3</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -784,13 +791,59 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Vertical Two Piece Mullion Screw Spline Assembly</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BE9-2511</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>8ft x 3</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>497</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>305.158</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr"/>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Bays Tall</t>
+        </is>
+      </c>
       <c r="B6" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Horizontal Horizontal Screw Spline Assembly</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>BE9-2515</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3ft x 4</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>527</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>323.578</v>
       </c>
     </row>
     <row r="7">
@@ -804,15 +857,26 @@
           <t>Equal distribution</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>COST/ELEVATION</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>TOTAL ELEVATION COST</t>
-        </is>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Horizontal Head</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>BE9-2514</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3ft x 4</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>444</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>272.616</v>
       </c>
     </row>
     <row r="8">
@@ -826,13 +890,26 @@
           <t>Equal distribution</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Thermal Sill Flashing</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BE9-2578</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>PROFILE COSTS</t>
-        </is>
+          <t>12ft</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>264</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0</v>
+        <v>162.096</v>
       </c>
     </row>
     <row r="9">
@@ -843,16 +920,29 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>36.00 in</t>
+          <t>144.00 in</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Horizontal Glass Stop (Use with BE9-2514, BE9-2515, BE9-2517)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>E9-2519</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ACCESSORY COSTS</t>
-        </is>
+          <t>3ft x 8</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>85.05</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0</v>
+        <v>52.2207</v>
       </c>
     </row>
     <row r="10">
@@ -866,13 +956,18 @@
           <t>96.00 in</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>GASKET COSTS</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>0</v>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Total Profile Cost</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>2805.05</v>
+      </c>
+      <c r="I10" s="9" t="n">
+        <v>1722.3007</v>
       </c>
     </row>
     <row r="11">
@@ -883,16 +978,13 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>24.00 sqft</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>DOOR COSTS</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>2258.25</v>
+          <t>96.00 sqft</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>ACCESSORIES</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -903,16 +995,33 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>24.00 sqft</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>GLASS COSTS</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>0</v>
+          <t>96.00 sqft</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -923,16 +1032,29 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>22.00 ft</t>
+          <t>40.00 ft</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>End Dam For Sill Flashing</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>E1-0199</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>FABRICATION COSTS</t>
-        </is>
+          <t>2.00 pcs</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>64.8</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0</v>
+        <v>39.7872</v>
       </c>
     </row>
     <row r="14">
@@ -943,11 +1065,30 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>22.00 ft</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="n"/>
-      <c r="I14" s="7" t="n"/>
+          <t>40.00 ft</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Water Deflector</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>E2-0047</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>8.00 pcs</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>73.066</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -957,21 +1098,533 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>1 x Medium Door ($2,258.25)
-  with: Exit Devices, Concealed Closer</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>#12 x 1-1/4” PHSMS Type AB, Zinc Plated Steel, For Screw Spline Attachment</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PC-1220</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>56.00 pcs</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>11.2362</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>#10-24 x 3/8” PHMS, Stainless Steel, For Attachment of Sill to Sill Flashing</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PM-1006-SS</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>12.00 pcs</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>46.65</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>28.6431</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Bay Distribution Diagram</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>*Note - C/L Dimensions</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>#12 x 3/4” UFHSMS Type A, Zinc Plated Steel For End Dam Attachment</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UA-1212</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>4.00 pcs</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>29.8404</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Setting Block Chair Use with E2-0177 Setting Block at Sill</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>E1-2530</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>8.00 pcs</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>22.104</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Side Block For Intermediate Vertical Shallow Pocket</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>E2-0166</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>6.00 pcs</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>47.2473</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Setting Block For Sill</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>E2-0177</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>8.00 pcs</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>47.2473</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1-1/8” “W” Side Block For Jamb</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>E2-0545</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>4.00 pcs</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>90.258</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1/2” “W” Side Block For Intermediate Vertical Deep Pocket</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>E2-0154</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>6.00 pcs</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>34.8138</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Setting Block For Intermediate Horizontal</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>E2-0611</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>8.00 pcs</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>58.4835</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>Total Accessory Cost</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>786.2</v>
+      </c>
+      <c r="I24" s="9" t="n">
+        <v>482.7268</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>GASKETS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Glazing Gasket For 1” Glazing</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>E2-0052</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>224.00 ft</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>405</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>248.67</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>Total Gasket Cost</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>405</v>
+      </c>
+      <c r="I28" s="9" t="n">
+        <v>248.67</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>GLASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Glass Area (Adjusted)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>83.75 sqft</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>879.375</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>879.375</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>Total Glass Cost</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>879.375</v>
+      </c>
+      <c r="I32" s="9" t="n">
+        <v>879.375</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>FABRICATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Joints Fabrication Labor</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>24.00 joints</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>360</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n"/>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>Total Fabrication Cost</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>360</v>
+      </c>
+      <c r="I36" s="9" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>COST/ELEVATION</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL ELEVATION COST</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>PROFILE COSTS</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>1722.3007</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ACCESSORY COSTS</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>482.7268</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>GASKET COSTS</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>248.67</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>GLASS COSTS</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>879.375</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>FABRICATION COSTS</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="G44" s="11" t="inlineStr">
         <is>
           <t>1 TOTAL COSTS</t>
         </is>
       </c>
-      <c r="I15" s="11" t="n">
-        <v>2258.25</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="G16" s="12" t="inlineStr">
+      <c r="I44" s="12" t="n">
+        <v>3693.0725</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="G45" s="13" t="inlineStr">
         <is>
           <t>*Note - Elevation costs based on discounted material costs</t>
         </is>
@@ -979,6 +1632,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -988,999 +1642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="2" customWidth="1" min="3" max="3"/>
-    <col width="2" customWidth="1" min="4" max="4"/>
-    <col width="99" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="2" customWidth="1" min="10" max="10"/>
-    <col width="2" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>System Input</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>YES 45TU FRONT SET(OG)</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>PROFILES</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Finish</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Part Number</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Total Quantity Required</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>Total List Cost</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>Discounted Total List Cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Elevation Type</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Vertical Sill/Jamb Screw Spline Assembly (Jamb) / Horizontal Sill/Jamb Screw Spline Assembly (Sill)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>BE9-2513</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>8ft, 8ft, 3ft, 3ft, 3ft, 3ft</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>921.8000000000002</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>565.9852000000001</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Total Count</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Vertical Flush Filler</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>E9-2512</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>8ft x 3</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>165</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>101.31</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Bays Wide</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Vertical Two Piece Mullion Screw Spline Assembly</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>BE9-2511</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>8ft x 3</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>546.7</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>335.6738</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Bays Tall</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Horizontal Horizontal Screw Spline Assembly</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>BE9-2515</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>3ft x 4</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>579.7</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>355.9358</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Custom Bay Widths</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Equal distribution</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Horizontal Head</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>BE9-2514</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>3ft x 4</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>488.4</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>299.8776</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Custom Bay Heights</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Equal distribution</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Thermal Sill Flashing</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>BE9-2578</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>12ft</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>290.4</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>178.3056</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Opening Width</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>144.00 in</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Horizontal Glass Stop (Use with BE9-2514, BE9-2515, BE9-2517)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>E9-2519</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>3ft x 8</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>93.55500000000001</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>57.44277</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Opening Height</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>96.00 in</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>Total Profile Cost</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>3085.555</v>
-      </c>
-      <c r="I10" s="9" t="n">
-        <v>1894.53077</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Sq Ft per Type</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>96.00 sqft</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>ACCESSORIES</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total Sq Ft</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>96.00 sqft</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Part Number</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>Total Quantity Required</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Total List Cost</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>Discounted Total List Cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Perimeter Ft</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>40.00 ft</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>End Dam For Sill Flashing</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>E1-0199</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2.00 pcs</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>39.7872</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Total Perimeter Ft</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>40.00 ft</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Water Deflector</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>E2-0047</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>8.00 pcs</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>119</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>73.066</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Doors</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>#12 x 1-1/4” PHSMS Type AB, Zinc Plated Steel, For Screw Spline Attachment</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>PC-1220</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>56.00 pcs</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>11.2362</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>#10-24 x 3/8” PHMS, Stainless Steel, For Attachment of Sill to Sill Flashing</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>PM-1006-SS</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>12.00 pcs</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>46.65</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>28.6431</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Bay Distribution Diagram</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>*Note - C/L Dimensions</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>#12 x 3/4” UFHSMS Type A, Zinc Plated Steel For End Dam Attachment</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>UA-1212</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>4.00 pcs</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>29.8404</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Setting Block Chair Use with E2-0177 Setting Block at Sill</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>E1-2530</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>8.00 pcs</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>22.104</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Side Block For Intermediate Vertical Shallow Pocket</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>E2-0166</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>6.00 pcs</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>76.95</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>47.2473</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Setting Block For Sill</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>E2-0177</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>8.00 pcs</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>76.95</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>47.2473</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>1-1/8” “W” Side Block For Jamb</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>E2-0545</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>4.00 pcs</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>147</v>
-      </c>
-      <c r="I21" s="5" t="n">
-        <v>90.258</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>1/2” “W” Side Block For Intermediate Vertical Deep Pocket</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>E2-0154</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>6.00 pcs</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>34.8138</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Setting Block For Intermediate Horizontal</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>E2-0611</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>8.00 pcs</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>95.25</v>
-      </c>
-      <c r="I23" s="5" t="n">
-        <v>58.4835</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>Total Accessory Cost</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="n">
-        <v>786.2</v>
-      </c>
-      <c r="I24" s="9" t="n">
-        <v>482.7268</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>GASKETS</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Part Number</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>Total Quantity Required</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Total List Cost</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>Discounted Total List Cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Glazing Gasket For 1” Glazing</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>E2-0052</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>224.00 ft</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>405</v>
-      </c>
-      <c r="I27" s="5" t="n">
-        <v>248.67</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>Total Gasket Cost</t>
-        </is>
-      </c>
-      <c r="H28" s="9" t="n">
-        <v>405</v>
-      </c>
-      <c r="I28" s="9" t="n">
-        <v>248.67</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>GLASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>Part Number</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>Total Quantity Required</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Total List Cost</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>Discounted Total List Cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Glass Area (Adjusted)</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>83.75 sqft</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>879.375</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>879.375</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="7" t="n"/>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>Total Glass Cost</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="n">
-        <v>879.375</v>
-      </c>
-      <c r="I32" s="9" t="n">
-        <v>879.375</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>FABRICATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>Part Number</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>Total Quantity Required</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>Total List Cost</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>Discounted Total List Cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Joints Fabrication Labor</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>24.00 joints</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>360</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="E36" s="7" t="n"/>
-      <c r="F36" s="7" t="n"/>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t>Total Fabrication Cost</t>
-        </is>
-      </c>
-      <c r="H36" s="9" t="n">
-        <v>360</v>
-      </c>
-      <c r="I36" s="9" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>COST/ELEVATION</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>TOTAL ELEVATION COST</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>PROFILE COSTS</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="n">
-        <v>1894.53077</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>ACCESSORY COSTS</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="n">
-        <v>482.7268</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>GASKET COSTS</t>
-        </is>
-      </c>
-      <c r="I41" s="5" t="n">
-        <v>248.67</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>GLASS COSTS</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="n">
-        <v>879.375</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>FABRICATION COSTS</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="G44" s="10" t="inlineStr">
-        <is>
-          <t>2 TOTAL COSTS</t>
-        </is>
-      </c>
-      <c r="I44" s="11" t="n">
-        <v>3865.30257</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>*Note - Elevation costs based on discounted material costs</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -1988,7 +1650,7 @@
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -2062,7 +1724,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BE9-2513 (black)</t>
+          <t>BE9-2513 (clear)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2081,10 +1743,10 @@
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>921.8000000000002</v>
+        <v>838</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>565.9852000000001</v>
+        <v>514.532</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2097,7 +1759,7 @@
         </is>
       </c>
       <c r="J3" s="5" t="n">
-        <v>235.8271666666667</v>
+        <v>214.3883333333333</v>
       </c>
     </row>
     <row r="4">
@@ -2108,7 +1770,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>E9-2512 (black)</t>
+          <t>E9-2512 (clear)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2127,10 +1789,10 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>101.31</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2154,7 +1816,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BE9-2511 (black)</t>
+          <t>BE9-2511 (clear)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2173,10 +1835,10 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>546.7</v>
+        <v>497</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>335.6738</v>
+        <v>305.158</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2200,7 +1862,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BE9-2515 (black)</t>
+          <t>BE9-2515 (clear)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2219,10 +1881,10 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>579.7</v>
+        <v>527</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>355.9358</v>
+        <v>323.578</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2235,7 +1897,7 @@
         </is>
       </c>
       <c r="J6" s="5" t="n">
-        <v>177.9679</v>
+        <v>161.789</v>
       </c>
     </row>
     <row r="7">
@@ -2246,7 +1908,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BE9-2514 (black)</t>
+          <t>BE9-2514 (clear)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2265,10 +1927,10 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>488.4</v>
+        <v>444</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>299.8776</v>
+        <v>272.616</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2281,7 +1943,7 @@
         </is>
       </c>
       <c r="J7" s="5" t="n">
-        <v>149.9388</v>
+        <v>136.308</v>
       </c>
     </row>
     <row r="8">
@@ -2292,7 +1954,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BE9-2578 (black)</t>
+          <t>BE9-2578 (clear)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2311,10 +1973,10 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>290.4</v>
+        <v>264</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>178.3056</v>
+        <v>162.096</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2327,7 +1989,7 @@
         </is>
       </c>
       <c r="J8" s="5" t="n">
-        <v>89.15280000000001</v>
+        <v>81.048</v>
       </c>
     </row>
     <row r="9">
@@ -2338,7 +2000,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>E9-2519 (black)</t>
+          <t>E9-2519 (clear)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2357,10 +2019,10 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>93.55500000000001</v>
+        <v>85.05</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>57.44277</v>
+        <v>52.2207</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -2387,15 +2049,15 @@
         </is>
       </c>
       <c r="F10" s="9" t="n">
-        <v>3085.555</v>
+        <v>2805.05</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>1894.53077</v>
+        <v>1722.3007</v>
       </c>
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="7" t="n"/>
       <c r="J10" s="9" t="n">
-        <v>652.8866666666668</v>
+        <v>593.5333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -3052,7 +2714,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>E2-0052 (black)</t>
+          <t>E2-0052 (clear)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3115,7 +2777,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>DOORS</t>
+          <t>GLASS</t>
         </is>
       </c>
     </row>
@@ -3174,12 +2836,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Door (3' X 8')</t>
+          <t>Glass Area (Adjusted)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Door (3' X 8')</t>
+          <t>Glass Area (Adjusted)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3189,19 +2851,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>$2258.25</t>
+          <t>$10.50</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.00 pcs</t>
+          <t>83.75 sqft</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>2258.25</v>
+        <v>879.375</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>2258.25</v>
+        <v>879.375</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -3224,14 +2886,14 @@
       <c r="D32" s="7" t="n"/>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Total Door Cost</t>
+          <t>Total Glass Cost</t>
         </is>
       </c>
       <c r="F32" s="9" t="n">
-        <v>2258.25</v>
+        <v>879.375</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>2258.25</v>
+        <v>879.375</v>
       </c>
       <c r="H32" s="7" t="n"/>
       <c r="I32" s="7" t="n"/>
@@ -3242,7 +2904,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>GLASS</t>
+          <t>LABOR</t>
         </is>
       </c>
     </row>
@@ -3301,12 +2963,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Glass Area (Adjusted)</t>
+          <t>Joints Fabrication Labor</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Glass Area (Adjusted)</t>
+          <t>Joints Fabrication Labor</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3316,19 +2978,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>$10.50</t>
+          <t>$15.00</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>83.75 sqft</t>
+          <t>24.00 joints</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>879.375</v>
+        <v>360</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>879.375</v>
+        <v>360</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -3351,14 +3013,14 @@
       <c r="D36" s="7" t="n"/>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Total Glass Cost</t>
+          <t>Total Labor Cost</t>
         </is>
       </c>
       <c r="F36" s="9" t="n">
-        <v>879.375</v>
+        <v>360</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>879.375</v>
+        <v>360</v>
       </c>
       <c r="H36" s="7" t="n"/>
       <c r="I36" s="7" t="n"/>
@@ -3367,289 +3029,162 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>LABOR</t>
-        </is>
-      </c>
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>COST OVERVIEW</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="n"/>
+      <c r="C37" s="16" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>Project Total Materials</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>Unit Price</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>Total Quantity Required</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>Total List Cost</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>Discounted Total List Cost</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>Residual Material Quantity</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>Residual Waste %</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>Residual Material Cost</t>
-        </is>
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>List Price Total:</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="n">
+        <v>5235.625</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Joints Fabrication Labor</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Joints Fabrication Labor</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>$15.00</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>24.00 joints</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>360</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>360</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="n">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>Discounted Total:</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="n">
+        <v>3693.0725</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>Residual/Waste Cost:</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="n">
+        <v>1130.844733333333</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t>Waste Percentage:</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="n"/>
+      <c r="C41" s="23" t="inlineStr">
+        <is>
+          <t>30.62%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>MISCELLANEOUS COSTS</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="n"/>
+      <c r="C42" s="26" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="27" t="inlineStr">
+        <is>
+          <t>(None configured)</t>
+        </is>
+      </c>
+      <c r="C43" s="28" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="29" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B44" s="30" t="n"/>
+      <c r="C44" s="31" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="7" t="n"/>
-      <c r="B40" s="7" t="n"/>
-      <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>Total Labor Cost</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="n">
-        <v>360</v>
-      </c>
-      <c r="G40" s="9" t="n">
-        <v>360</v>
-      </c>
-      <c r="H40" s="7" t="n"/>
-      <c r="I40" s="7" t="n"/>
-      <c r="J40" s="9" t="n">
+    <row r="45">
+      <c r="A45" s="32" t="inlineStr">
+        <is>
+          <t>MARKUPS / PROFIT</t>
+        </is>
+      </c>
+      <c r="B45" s="33" t="n"/>
+      <c r="C45" s="34" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="27" t="inlineStr">
+        <is>
+          <t>(None configured)</t>
+        </is>
+      </c>
+      <c r="C46" s="28" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="29" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B47" s="30" t="n"/>
+      <c r="C47" s="31" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="14" t="inlineStr">
-        <is>
-          <t>COST OVERVIEW</t>
-        </is>
-      </c>
-      <c r="B41" s="15" t="n"/>
-      <c r="C41" s="16" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>List Price Total:</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="n">
-        <v>7774.38</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="19" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="35" t="inlineStr">
+        <is>
+          <t>PROJECT TOTAL</t>
+        </is>
+      </c>
+      <c r="B48" s="36" t="n"/>
+      <c r="C48" s="37" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="38" t="inlineStr">
         <is>
           <t>Discounted Total:</t>
         </is>
       </c>
-      <c r="C43" s="20" t="n">
-        <v>6123.55257</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="17" t="inlineStr">
-        <is>
-          <t>Residual/Waste Cost:</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="n">
-        <v>1190.198066666667</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="21" t="inlineStr">
-        <is>
-          <t>Waste Percentage:</t>
-        </is>
-      </c>
-      <c r="B45" s="22" t="n"/>
-      <c r="C45" s="23" t="inlineStr">
-        <is>
-          <t>19.44%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="24" t="inlineStr">
-        <is>
-          <t>MISCELLANEOUS COSTS</t>
-        </is>
-      </c>
-      <c r="B46" s="25" t="n"/>
-      <c r="C46" s="26" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="27" t="inlineStr">
-        <is>
-          <t>(None configured)</t>
-        </is>
-      </c>
-      <c r="C47" s="28" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="29" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="B48" s="30" t="n"/>
-      <c r="C48" s="31" t="n">
+      <c r="B49" s="39" t="n"/>
+      <c r="C49" s="40" t="n">
+        <v>3693.0725</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>+ Miscellaneous:</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="32" t="inlineStr">
-        <is>
-          <t>MARKUPS / PROFIT</t>
-        </is>
-      </c>
-      <c r="B49" s="33" t="n"/>
-      <c r="C49" s="34" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="27" t="inlineStr">
-        <is>
-          <t>(None configured)</t>
-        </is>
-      </c>
-      <c r="C50" s="28" t="n"/>
-    </row>
     <row r="51">
-      <c r="A51" s="29" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="B51" s="30" t="n"/>
-      <c r="C51" s="31" t="n">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>+ Markups:</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="35" t="inlineStr">
-        <is>
-          <t>PROJECT TOTAL</t>
-        </is>
-      </c>
-      <c r="B52" s="36" t="n"/>
-      <c r="C52" s="37" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="38" t="inlineStr">
-        <is>
-          <t>Discounted Total:</t>
-        </is>
-      </c>
-      <c r="B53" s="39" t="n"/>
-      <c r="C53" s="40" t="n">
-        <v>6123.55257</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="17" t="inlineStr">
-        <is>
-          <t>+ Miscellaneous:</t>
-        </is>
-      </c>
-      <c r="C54" s="18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="17" t="inlineStr">
-        <is>
-          <t>+ Markups:</t>
-        </is>
-      </c>
-      <c r="C55" s="18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="41" t="inlineStr">
+      <c r="A52" s="41" t="inlineStr">
         <is>
           <t>GRAND TOTAL:</t>
         </is>
       </c>
-      <c r="B56" s="42" t="n"/>
-      <c r="C56" s="43" t="n">
-        <v>6123.55257</v>
+      <c r="B52" s="42" t="n"/>
+      <c r="C52" s="43" t="n">
+        <v>3693.0725</v>
       </c>
     </row>
   </sheetData>

--- a/.files/test_Report.xlsx
+++ b/.files/test_Report.xlsx
@@ -8,7 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00_-"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,6 +48,9 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -161,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -199,6 +204,8 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -302,10 +309,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3429000" cy="2571750"/>
+    <ext cx="2667000" cy="2000250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -327,6 +334,36 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2667000" cy="2000250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -648,8 +685,8 @@
   <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="2" customWidth="1" min="3" max="3"/>
     <col width="2" customWidth="1" min="4" max="4"/>
     <col width="99" customWidth="1" min="5" max="5"/>
@@ -1119,6 +1156,16 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Bay Distribution Diagram</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>*Note - C/L Dimensions</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>#10-24 x 3/8” PHMS, Stainless Steel, For Attachment of Sill to Sill Flashing</t>
@@ -1142,16 +1189,6 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Bay Distribution Diagram</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>*Note - C/L Dimensions</t>
-        </is>
-      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>#12 x 3/4” UFHSMS Type A, Zinc Plated Steel For End Dam Attachment</t>
@@ -1637,7 +1674,1515 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:K54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="2" customWidth="1" min="3" max="3"/>
+    <col width="2" customWidth="1" min="4" max="4"/>
+    <col width="99" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="2" customWidth="1" min="10" max="10"/>
+    <col width="2" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>System Input</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>YES 45TU FRONT SET(OG)</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>PROFILES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Finish</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Elevation Type</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Vertical Sill/Jamb Screw Spline Assembly (Jamb) / Horizontal Sill/Jamb Screw Spline Assembly (Sill)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>BE9-2513</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8ft, 8ft, 3ft, 3ft, 3ft, 3ft</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>838</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>514.532</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Total Count</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Vertical Flush Filler</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>E9-2512</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8ft x 3</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>92.09999999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Bays Wide</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Vertical Two Piece Mullion Screw Spline Assembly</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BE9-2511</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>8ft x 3</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>497</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>305.158</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Bays Tall</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Horizontal Horizontal Screw Spline Assembly</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>BE9-2515</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3ft x 4</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>527</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>323.578</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Custom Bay Widths</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Equal distribution</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Horizontal Head</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>BE9-2514</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3ft x 4</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>444</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>272.616</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Custom Bay Heights</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Equal distribution</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Thermal Sill Flashing</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BE9-2578</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>12ft</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>264</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>162.096</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Opening Width</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>144.00 in</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Horizontal Glass Stop (Use with BE9-2514, BE9-2515, BE9-2517)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>E9-2519</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3ft x 8</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>85.05</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>52.2207</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Opening Height</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>96.00 in</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Total Profile Cost</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>2805.05</v>
+      </c>
+      <c r="I10" s="9" t="n">
+        <v>1722.3007</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Sq Ft per Type</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>96.00 sqft</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>ACCESSORIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Total Sq Ft</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>96.00 sqft</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Perimeter Ft</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>40.00 ft</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>End Dam For Sill Flashing</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>E1-0199</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2.00 pcs</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>39.7872</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Total Perimeter Ft</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>40.00 ft</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Water Deflector</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>E2-0047</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>8.00 pcs</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>73.066</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Doors</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>1 x Wide Door ($2,224.00)
+  with: Extended Ladder Pull (B2B), Latch Lock w/ Lever Handle, Extended Ladder Pull (Single)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>#12 x 1-1/4” PHSMS Type AB, Zinc Plated Steel, For Screw Spline Attachment</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PC-1220</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>56.00 pcs</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>11.2362</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Bay Distribution Diagram</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>*Note - C/L Dimensions</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>#10-24 x 3/8” PHMS, Stainless Steel, For Attachment of Sill to Sill Flashing</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PM-1006-SS</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>12.00 pcs</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>46.65</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>28.6431</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>#12 x 3/4” UFHSMS Type A, Zinc Plated Steel For End Dam Attachment</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UA-1212</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>4.00 pcs</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>29.8404</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Setting Block Chair Use with E2-0177 Setting Block at Sill</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>E1-2530</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>8.00 pcs</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>22.104</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Side Block For Intermediate Vertical Shallow Pocket</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>E2-0166</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>6.00 pcs</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>47.2473</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Setting Block For Sill</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>E2-0177</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>8.00 pcs</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>47.2473</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1-1/8” “W” Side Block For Jamb</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>E2-0545</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>4.00 pcs</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>90.258</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1/2” “W” Side Block For Intermediate Vertical Deep Pocket</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>E2-0154</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>6.00 pcs</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>34.8138</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Setting Block For Intermediate Horizontal</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>E2-0611</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>8.00 pcs</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>58.4835</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>Total Accessory Cost</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>786.2</v>
+      </c>
+      <c r="I24" s="9" t="n">
+        <v>482.7268</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>GASKETS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Glazing Gasket For 1” Glazing</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>E2-0052</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>224.00 ft</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>405</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>248.67</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>Total Gasket Cost</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>405</v>
+      </c>
+      <c r="I28" s="9" t="n">
+        <v>248.67</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>DOORS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Door (3' X 8')</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1.00 pcs</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>2224</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>Total Door Cost</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>2224</v>
+      </c>
+      <c r="I32" s="9" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>GLASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Glass Area (Adjusted)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>73.80 sqft</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>774.9</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>774.9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n"/>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>Total Glass Cost</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>774.9</v>
+      </c>
+      <c r="I36" s="9" t="n">
+        <v>774.9</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>CALCULATIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Door Area (to subtract from glass)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>24.00 sqft</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="E40" s="7" t="n"/>
+      <c r="F40" s="7" t="n"/>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>Total Calculations Cost</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>FABRICATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Joints Fabrication Labor</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>24.00 joints</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>360</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="E44" s="7" t="n"/>
+      <c r="F44" s="7" t="n"/>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>Total Fabrication Cost</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="n">
+        <v>360</v>
+      </c>
+      <c r="I44" s="9" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>COST/ELEVATION</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL ELEVATION COST</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>PROFILE COSTS</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>1722.3007</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ACCESSORY COSTS</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>482.7268</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>GASKET COSTS</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>248.67</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>DOOR COSTS</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>GLASS COSTS</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>774.9</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>FABRICATION COSTS</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="G53" s="11" t="inlineStr">
+        <is>
+          <t>2 TOTAL COSTS</t>
+        </is>
+      </c>
+      <c r="I53" s="12" t="n">
+        <v>5812.5975</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="G54" s="13" t="inlineStr">
+        <is>
+          <t>*Note - Elevation costs based on discounted material costs</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="2" customWidth="1" min="3" max="3"/>
+    <col width="2" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="2" customWidth="1" min="10" max="10"/>
+    <col width="2" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>System Input</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Door Only</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>DOORS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Finish</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Elevation Type</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Door (6' X 9')</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3.00 pcs</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>13302.75</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>13302.75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Total Count</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Door (3' X 7')</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2.00 pcs</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>1760</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Bays Wide</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Total Door Cost</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>15062.75</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>15062.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Bays Tall</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Equal distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Custom Bay Heights</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Equal distribution</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>COST/ELEVATION</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL ELEVATION COST</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Opening Width</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>72.00 in</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>PROFILE COSTS</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Opening Height</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>108.00 in</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ACCESSORY COSTS</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Sq Ft per Type</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>54.00 sqft</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>GASKET COSTS</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Total Sq Ft</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>54.00 sqft</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>DOOR COSTS</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>15062.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Perimeter Ft</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>30.00 ft</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>GLASS COSTS</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Total Perimeter Ft</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>30.00 ft</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>FABRICATION COSTS</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Doors</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>3 x Medium Door ($4,434.25)
+  with: Exit Devices, Electric Strike; 
+2 x Narrow Door ($880.00)</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>3 TOTAL COSTS</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>15062.75</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>*Note - Elevation costs based on discounted material costs</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -1645,7 +3190,7 @@
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -1724,37 +3269,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.00 ft</t>
+          <t>56.00 ft</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2 (24ft per)</t>
+          <t>3 (24ft per)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8ft x2, 3ft x4</t>
+          <t>8ft x4, 3ft x8</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>838</v>
+        <v>1257</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>514.532</v>
+        <v>771.798</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>18ft x1, 2ft x1</t>
+          <t>16ft x1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.67%</t>
+          <t>22.22%</t>
         </is>
       </c>
       <c r="J3" s="5" t="n">
-        <v>214.3883333333333</v>
+        <v>171.5106666666667</v>
       </c>
     </row>
     <row r="4">
@@ -1770,24 +3315,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>24.00 ft</t>
+          <t>48.00 ft</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1 (24ft per)</t>
+          <t>2 (24ft per)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8ft x3</t>
+          <t>8ft x6</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>92.09999999999999</v>
+        <v>184.2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1816,24 +3361,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24.00 ft</t>
+          <t>48.00 ft</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1 (24ft per)</t>
+          <t>2 (24ft per)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8ft x3</t>
+          <t>8ft x6</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>497</v>
+        <v>994</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>305.158</v>
+        <v>610.316</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1862,7 +3407,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12.00 ft</t>
+          <t>24.00 ft</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1872,7 +3417,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3ft x4</t>
+          <t>3ft x8</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
@@ -1883,16 +3428,16 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>12ft x1</t>
+          <t>0.00 ft</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J6" s="5" t="n">
-        <v>161.789</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1908,7 +3453,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12.00 ft</t>
+          <t>24.00 ft</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1918,7 +3463,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3ft x4</t>
+          <t>3ft x8</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
@@ -1929,16 +3474,16 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>12ft x1</t>
+          <t>0.00 ft</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J7" s="5" t="n">
-        <v>136.308</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1954,7 +3499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12.00 ft</t>
+          <t>24.00 ft</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1964,7 +3509,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12ft</t>
+          <t>12ft x2</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
@@ -1975,16 +3520,16 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>12ft x1</t>
+          <t>0.00 ft</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J8" s="5" t="n">
-        <v>81.048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2000,24 +3545,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>24.00 ft</t>
+          <t>48.00 ft</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1 (24ft per)</t>
+          <t>2 (24ft per)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3ft x8</t>
+          <t>3ft x16</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>85.05</v>
+        <v>170.1</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>52.2207</v>
+        <v>104.4414</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -2044,15 +3589,15 @@
         </is>
       </c>
       <c r="F10" s="9" t="n">
-        <v>2805.05</v>
+        <v>3956.1</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>1722.3007</v>
+        <v>2429.0454</v>
       </c>
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="7" t="n"/>
       <c r="J10" s="9" t="n">
-        <v>593.5333333333333</v>
+        <v>171.5106666666667</v>
       </c>
     </row>
     <row r="11">
@@ -2127,7 +3672,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.00 pcs</t>
+          <t>4.00 pcs</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2148,16 +3693,16 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>18.00 pcs</t>
+          <t>16.00 pcs</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>90.00%</t>
+          <t>80.00%</t>
         </is>
       </c>
       <c r="J13" s="5" t="n">
-        <v>35.80848</v>
+        <v>31.82976</v>
       </c>
     </row>
     <row r="14">
@@ -2173,7 +3718,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8.00 pcs</t>
+          <t>16.00 pcs</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2194,16 +3739,16 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>42.00 pcs</t>
+          <t>34.00 pcs</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>84.00%</t>
+          <t>68.00%</t>
         </is>
       </c>
       <c r="J14" s="5" t="n">
-        <v>61.37544</v>
+        <v>49.68488</v>
       </c>
     </row>
     <row r="15">
@@ -2219,7 +3764,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>56.00 pcs</t>
+          <t>112.00 pcs</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2229,18 +3774,18 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1 order</t>
+          <t>2 orders</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>18.3</v>
+        <v>36.6</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>11.2362</v>
+        <v>22.4724</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>44.00 pcs</t>
+          <t>88.00 pcs</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2249,7 +3794,7 @@
         </is>
       </c>
       <c r="J15" s="5" t="n">
-        <v>4.943928</v>
+        <v>9.887855999999999</v>
       </c>
     </row>
     <row r="16">
@@ -2265,7 +3810,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>12.00 pcs</t>
+          <t>24.00 pcs</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2286,16 +3831,16 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>88.00 pcs</t>
+          <t>76.00 pcs</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>88.00%</t>
+          <t>76.00%</t>
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>25.205928</v>
+        <v>21.768756</v>
       </c>
     </row>
     <row r="17">
@@ -2311,7 +3856,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4.00 pcs</t>
+          <t>8.00 pcs</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2332,16 +3877,16 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>96.00 pcs</t>
+          <t>92.00 pcs</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>96.00%</t>
+          <t>92.00%</t>
         </is>
       </c>
       <c r="J17" s="5" t="n">
-        <v>28.646784</v>
+        <v>27.453168</v>
       </c>
     </row>
     <row r="18">
@@ -2357,7 +3902,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>8.00 pcs</t>
+          <t>16.00 pcs</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2367,14 +3912,14 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8 orders</t>
+          <t>16 orders</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>22.104</v>
+        <v>44.208</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2403,7 +3948,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6.00 pcs</t>
+          <t>12.00 pcs</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2424,16 +3969,16 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>44.00 pcs</t>
+          <t>38.00 pcs</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>88.00%</t>
+          <t>76.00%</t>
         </is>
       </c>
       <c r="J19" s="5" t="n">
-        <v>41.57762400000001</v>
+        <v>35.907948</v>
       </c>
     </row>
     <row r="20">
@@ -2449,7 +3994,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>8.00 pcs</t>
+          <t>16.00 pcs</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2470,16 +4015,16 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>42.00 pcs</t>
+          <t>34.00 pcs</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>84.00%</t>
+          <t>68.00%</t>
         </is>
       </c>
       <c r="J20" s="5" t="n">
-        <v>39.687732</v>
+        <v>32.12816400000001</v>
       </c>
     </row>
     <row r="21">
@@ -2495,7 +4040,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4.00 pcs</t>
+          <t>8.00 pcs</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2516,16 +4061,16 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>46.00 pcs</t>
+          <t>42.00 pcs</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>92.00%</t>
+          <t>84.00%</t>
         </is>
       </c>
       <c r="J21" s="5" t="n">
-        <v>83.03736000000001</v>
+        <v>75.81672</v>
       </c>
     </row>
     <row r="22">
@@ -2541,7 +4086,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>6.00 pcs</t>
+          <t>12.00 pcs</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2562,16 +4107,16 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>44.00 pcs</t>
+          <t>38.00 pcs</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>88.00%</t>
+          <t>76.00%</t>
         </is>
       </c>
       <c r="J22" s="5" t="n">
-        <v>30.63614400000001</v>
+        <v>26.458488</v>
       </c>
     </row>
     <row r="23">
@@ -2587,7 +4132,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>8.00 pcs</t>
+          <t>16.00 pcs</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2608,16 +4153,16 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>42.00 pcs</t>
+          <t>34.00 pcs</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>84.00%</t>
+          <t>68.00%</t>
         </is>
       </c>
       <c r="J23" s="5" t="n">
-        <v>49.12614</v>
+        <v>39.76878</v>
       </c>
     </row>
     <row r="24">
@@ -2631,15 +4176,15 @@
         </is>
       </c>
       <c r="F24" s="9" t="n">
-        <v>786.2</v>
+        <v>840.5000000000001</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>482.7268</v>
+        <v>516.067</v>
       </c>
       <c r="H24" s="7" t="n"/>
       <c r="I24" s="7" t="n"/>
       <c r="J24" s="9" t="n">
-        <v>400.04556</v>
+        <v>350.70452</v>
       </c>
     </row>
     <row r="25">
@@ -2714,7 +4259,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>224.00 ft</t>
+          <t>448.00 ft</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2724,7 +4269,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>224ft</t>
+          <t>224ft x2</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
@@ -2735,16 +4280,16 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>276ft x1</t>
+          <t>52ft x1</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>55.20%</t>
+          <t>10.40%</t>
         </is>
       </c>
       <c r="J27" s="5" t="n">
-        <v>137.26584</v>
+        <v>25.86168</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +4311,13 @@
       <c r="H28" s="7" t="n"/>
       <c r="I28" s="7" t="n"/>
       <c r="J28" s="9" t="n">
-        <v>137.26584</v>
+        <v>25.86168</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>GLASS</t>
+          <t>DOORS</t>
         </is>
       </c>
     </row>
@@ -2831,12 +4376,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Glass Area (Adjusted)</t>
+          <t>Door (6' X 9')</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Glass Area (Adjusted)</t>
+          <t>Door (6' X 9')</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2846,19 +4391,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>$10.50</t>
+          <t>$4434.25</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>83.75 sqft</t>
+          <t>3.00 pcs</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>879.375</v>
+        <v>13302.75</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>879.375</v>
+        <v>13302.75</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2875,425 +4420,530 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="n"/>
-      <c r="B32" s="7" t="n"/>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Door (3' X 7')</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Door (3' X 7')</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>$880.00</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2.00 pcs</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>1760</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>1760</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Door (3' X 8')</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Door (3' X 8')</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>$2224.00</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.00 pcs</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>2224</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>2224</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n"/>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>Total Door Cost</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>17286.75</v>
+      </c>
+      <c r="G34" s="9" t="n">
+        <v>17286.75</v>
+      </c>
+      <c r="H34" s="7" t="n"/>
+      <c r="I34" s="7" t="n"/>
+      <c r="J34" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>GLASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Project Total Materials</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Unit Price</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Residual Material Quantity</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>Residual Waste %</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>Residual Material Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Glass Area (Adjusted)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Glass Area (Adjusted)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>$10.50</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>157.55 sqft</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>1654.275</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>1654.275</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n"/>
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>Total Glass Cost</t>
         </is>
       </c>
-      <c r="F32" s="9" t="n">
-        <v>879.375</v>
-      </c>
-      <c r="G32" s="9" t="n">
-        <v>879.375</v>
-      </c>
-      <c r="H32" s="7" t="n"/>
-      <c r="I32" s="7" t="n"/>
-      <c r="J32" s="9" t="n">
+      <c r="F38" s="9" t="n">
+        <v>1654.275</v>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>1654.275</v>
+      </c>
+      <c r="H38" s="7" t="n"/>
+      <c r="I38" s="7" t="n"/>
+      <c r="J38" s="9" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>LABOR</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Project Total Materials</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>Unit Price</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>Total Quantity Required</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>Total List Cost</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>Discounted Total List Cost</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>Residual Material Quantity</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr">
+      <c r="I40" s="4" t="inlineStr">
         <is>
           <t>Residual Waste %</t>
         </is>
       </c>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>Residual Material Cost</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Joints Fabrication Labor</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Joints Fabrication Labor</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>$15.00</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>24.00 joints</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>360</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>360</v>
-      </c>
-      <c r="H35" t="inlineStr">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>48.00 joints</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>720</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>720</v>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J35" s="5" t="n">
+      <c r="J41" s="5" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="7" t="n"/>
-      <c r="B36" s="7" t="n"/>
-      <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="n"/>
-      <c r="E36" s="8" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="7" t="n"/>
+      <c r="B42" s="7" t="n"/>
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>Total Labor Cost</t>
         </is>
       </c>
-      <c r="F36" s="9" t="n">
-        <v>360</v>
-      </c>
-      <c r="G36" s="9" t="n">
-        <v>360</v>
-      </c>
-      <c r="H36" s="7" t="n"/>
-      <c r="I36" s="7" t="n"/>
-      <c r="J36" s="9" t="n">
+      <c r="F42" s="9" t="n">
+        <v>720</v>
+      </c>
+      <c r="G42" s="9" t="n">
+        <v>720</v>
+      </c>
+      <c r="H42" s="7" t="n"/>
+      <c r="I42" s="7" t="n"/>
+      <c r="J42" s="9" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>COST OVERVIEW</t>
         </is>
       </c>
-      <c r="B37" s="15" t="n"/>
-      <c r="C37" s="16" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>List Price Total:</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="n">
-        <v>5235.625</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>Discounted Total:</t>
-        </is>
-      </c>
-      <c r="C39" s="20" t="n">
-        <v>3693.0725</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>Residual/Waste Cost:</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="n">
-        <v>1130.844733333333</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="21" t="inlineStr">
-        <is>
-          <t>Waste Percentage:</t>
-        </is>
-      </c>
-      <c r="B41" s="22" t="n"/>
-      <c r="C41" s="23" t="inlineStr">
-        <is>
-          <t>30.62%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="24" t="inlineStr">
-        <is>
-          <t>ADDITIONAL COSTS</t>
-        </is>
-      </c>
-      <c r="B42" s="25" t="n"/>
-      <c r="C42" s="26" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>Overhead Materials</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="n">
-        <v>184.653625</v>
-      </c>
+      <c r="B43" s="15" t="n"/>
+      <c r="C43" s="16" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t>Overhead Labor</t>
+          <t>List Price Total:</t>
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>184.653625</v>
+        <v>24862.625</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="inlineStr">
-        <is>
-          <t>Admin and Management</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="n">
-        <v>184.653625</v>
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>Discounted Total:</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="n">
+        <v>22854.8074</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Residual/Waste Cost:</t>
         </is>
       </c>
       <c r="C46" s="18" t="n">
-        <v>184.653625</v>
+        <v>548.0768666666665</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="17" t="inlineStr">
-        <is>
-          <t>Packaging Materials</t>
-        </is>
-      </c>
-      <c r="C47" s="18" t="n">
-        <v>184.653625</v>
+      <c r="A47" s="21" t="inlineStr">
+        <is>
+          <t>Waste Percentage:</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="n"/>
+      <c r="C47" s="23" t="inlineStr">
+        <is>
+          <t>2.40%</t>
+        </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="17" t="inlineStr">
-        <is>
-          <t>Shipping and Transport</t>
-        </is>
-      </c>
-      <c r="C48" s="18" t="n">
-        <v>184.653625</v>
-      </c>
+      <c r="A48" s="24" t="inlineStr">
+        <is>
+          <t>ADDITIONAL COSTS</t>
+        </is>
+      </c>
+      <c r="B48" s="25" t="n"/>
+      <c r="C48" s="26" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="17" t="inlineStr">
-        <is>
-          <t>Commissions</t>
-        </is>
-      </c>
-      <c r="C49" s="18" t="n">
-        <v>184.653625</v>
-      </c>
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t>(None configured)</t>
+        </is>
+      </c>
+      <c r="C49" s="28" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="27" t="inlineStr">
+      <c r="A50" s="29" t="inlineStr">
         <is>
           <t>SUBTOTAL</t>
         </is>
       </c>
-      <c r="B50" s="28" t="n"/>
-      <c r="C50" s="29" t="n">
-        <v>1292.575375</v>
+      <c r="B50" s="30" t="n"/>
+      <c r="C50" s="31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="30" t="inlineStr">
+      <c r="A51" s="32" t="inlineStr">
         <is>
           <t>MARKUPS / PROFIT</t>
         </is>
       </c>
-      <c r="B51" s="31" t="n"/>
-      <c r="C51" s="32" t="n"/>
+      <c r="B51" s="33" t="n"/>
+      <c r="C51" s="34" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="17" t="inlineStr">
-        <is>
-          <t>Profit on Material</t>
-        </is>
-      </c>
-      <c r="C52" s="18" t="n">
-        <v>122.684875</v>
-      </c>
+      <c r="A52" s="27" t="inlineStr">
+        <is>
+          <t>(None configured)</t>
+        </is>
+      </c>
+      <c r="C52" s="28" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="17" t="inlineStr">
-        <is>
-          <t>Profit on Waste</t>
-        </is>
-      </c>
-      <c r="C53" s="18" t="n">
-        <v>56.54223666666667</v>
+      <c r="A53" s="29" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B53" s="30" t="n"/>
+      <c r="C53" s="31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="17" t="inlineStr">
-        <is>
-          <t>Profit on Glass Purchase</t>
-        </is>
-      </c>
-      <c r="C54" s="18" t="n">
-        <v>43.96875</v>
-      </c>
+      <c r="A54" s="35" t="inlineStr">
+        <is>
+          <t>PROJECT TOTAL</t>
+        </is>
+      </c>
+      <c r="B54" s="36" t="n"/>
+      <c r="C54" s="37" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="17" t="inlineStr">
-        <is>
-          <t>Profit on Wages</t>
-        </is>
-      </c>
-      <c r="C55" s="18" t="n">
-        <v>18</v>
+      <c r="A55" s="38" t="inlineStr">
+        <is>
+          <t>Discounted Total:</t>
+        </is>
+      </c>
+      <c r="B55" s="39" t="n"/>
+      <c r="C55" s="40" t="n">
+        <v>22854.8074</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="17" t="inlineStr">
         <is>
-          <t>Planning / Technical Office</t>
+          <t>+ Additional:</t>
         </is>
       </c>
       <c r="C56" s="18" t="n">
-        <v>184.653625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="17" t="inlineStr">
         <is>
-          <t>Commission</t>
+          <t>+ Markups:</t>
         </is>
       </c>
       <c r="C57" s="18" t="n">
-        <v>184.653625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="27" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="B58" s="28" t="n"/>
-      <c r="C58" s="29" t="n">
-        <v>610.5031116666668</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="33" t="inlineStr">
-        <is>
-          <t>PROJECT TOTAL</t>
-        </is>
-      </c>
-      <c r="B59" s="34" t="n"/>
-      <c r="C59" s="35" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="36" t="inlineStr">
-        <is>
-          <t>Discounted Total:</t>
-        </is>
-      </c>
-      <c r="B60" s="37" t="n"/>
-      <c r="C60" s="38" t="n">
-        <v>3693.0725</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="17" t="inlineStr">
-        <is>
-          <t>+ Additional:</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="n">
-        <v>1292.575375</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="17" t="inlineStr">
-        <is>
-          <t>+ Markups:</t>
-        </is>
-      </c>
-      <c r="C62" s="18" t="n">
-        <v>610.5031116666668</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="39" t="inlineStr">
+      <c r="A58" s="41" t="inlineStr">
         <is>
           <t>GRAND TOTAL:</t>
         </is>
       </c>
-      <c r="B63" s="40" t="n"/>
-      <c r="C63" s="41" t="n">
-        <v>5596.150986666667</v>
+      <c r="B58" s="42" t="n"/>
+      <c r="C58" s="43" t="n">
+        <v>22854.8074</v>
       </c>
     </row>
   </sheetData>
